--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/TENNESSEE_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/TENNESSEE_2014.xlsx
@@ -1021,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="D37">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="38">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C167">
@@ -4891,7 +4891,7 @@
         <v>11</v>
       </c>
       <c r="D252">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="253">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C263">
@@ -5215,7 +5215,7 @@
         <v>11</v>
       </c>
       <c r="D270">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="271">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C273">
@@ -6223,7 +6223,7 @@
         <v>11</v>
       </c>
       <c r="D326">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="327">
@@ -9049,7 +9049,7 @@
         <v>11</v>
       </c>
       <c r="D483">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="484">
@@ -10075,7 +10075,7 @@
         <v>11</v>
       </c>
       <c r="D540">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="541">
@@ -10903,7 +10903,7 @@
         <v>11</v>
       </c>
       <c r="D586">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="587">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C637">
@@ -12667,7 +12667,7 @@
         <v>11</v>
       </c>
       <c r="D684">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="685">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C737">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C738">
@@ -13999,7 +13999,7 @@
         <v>11</v>
       </c>
       <c r="D758">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="759">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C770">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C771">
@@ -16987,7 +16987,7 @@
         <v>11</v>
       </c>
       <c r="D924">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="925">
@@ -17257,7 +17257,7 @@
         <v>11</v>
       </c>
       <c r="D939">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="940">
@@ -17545,7 +17545,7 @@
         <v>11</v>
       </c>
       <c r="D955">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="956">
@@ -19651,7 +19651,7 @@
         <v>11</v>
       </c>
       <c r="D1072">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="1073">
@@ -20299,7 +20299,7 @@
         <v>11</v>
       </c>
       <c r="D1108">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="1109">
@@ -20821,7 +20821,7 @@
         <v>11</v>
       </c>
       <c r="D1137">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="1138">
@@ -20839,7 +20839,7 @@
         <v>11</v>
       </c>
       <c r="D1138">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="1139">
@@ -22405,7 +22405,7 @@
         <v>11</v>
       </c>
       <c r="D1225">
-        <v>0.000955607679611</v>
+        <v>0.0009556076796110002</v>
       </c>
     </row>
     <row r="1226">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="B1226" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1226">
